--- a/branches/dev/observations-summary.xlsx
+++ b/branches/dev/observations-summary.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1166" uniqueCount="290">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="814" uniqueCount="238">
   <si>
     <t>Profile</t>
   </si>
@@ -173,15 +173,6 @@
     <t>null#251845003, null#9203-1, null#null</t>
   </si>
   <si>
-    <t>mii-pr-icu-bilanz-einfuhr-abgepumpte-muttermilch</t>
-  </si>
-  <si>
-    <t>MII PR ICU Bilanz Einfuhr Abgepumpte Muttermilch</t>
-  </si>
-  <si>
-    <t>null#819975003, null#null, null#null</t>
-  </si>
-  <si>
     <t>mii-pr-icu-bilanz-einfuhr-enterale-fluessigkeit</t>
   </si>
   <si>
@@ -200,54 +191,6 @@
     <t>null#251852001, null#9103-3, null#null</t>
   </si>
   <si>
-    <t>mii-pr-icu-bilanz-einfuhr-kalorien-24h</t>
-  </si>
-  <si>
-    <t>MII PR ICU Bilanz Einfuhr Kalorien 24h</t>
-  </si>
-  <si>
-    <t>null#787787004, null#9057-1, null#null</t>
-  </si>
-  <si>
-    <t>Periodĵ</t>
-  </si>
-  <si>
-    <t>mii-pr-icu-bilanz-einfuhr-muttermilch</t>
-  </si>
-  <si>
-    <t>MII PR ICU Bilanz Einfuhr Muttermilch</t>
-  </si>
-  <si>
-    <t>null#1204299001, null#null, null#null</t>
-  </si>
-  <si>
-    <t>mii-pr-icu-bilanz-einfuhr-orale-fluessigkeit</t>
-  </si>
-  <si>
-    <t>MII PR ICU Bilanz Einfuhr Orale Fluessigkeit</t>
-  </si>
-  <si>
-    <t>null#251853006, null#9000-1, null#null</t>
-  </si>
-  <si>
-    <t>mii-pr-icu-bilanz-einfuhr-saeuglingsnahrung</t>
-  </si>
-  <si>
-    <t>MII PR ICU Bilanz Einfuhr Saeuglingsnahrung</t>
-  </si>
-  <si>
-    <t>null#1204305004, null#null, null#null</t>
-  </si>
-  <si>
-    <t>mii-pr-icu-bilanz-einfuhr-spendermilch</t>
-  </si>
-  <si>
-    <t>MII PR ICU Bilanz Einfuhr Spendermilch</t>
-  </si>
-  <si>
-    <t>null#819973005, null#null, null#null</t>
-  </si>
-  <si>
     <t>mii-pr-icu-bilanz-tagesbilanz-fluessigkeit</t>
   </si>
   <si>
@@ -419,15 +362,6 @@
     <t>null#8306-3, null#1149101003</t>
   </si>
   <si>
-    <t>mii-pr-icu-muv-kohlendioxid-produktion</t>
-  </si>
-  <si>
-    <t>MII PR ICU MUV Kohlendioxid Produktion</t>
-  </si>
-  <si>
-    <t>null#60825-7, null#251408004</t>
-  </si>
-  <si>
     <t>mii-pr-icu-muv-kopfumfang</t>
   </si>
   <si>
@@ -461,36 +395,27 @@
     <t>Quantityĵ, CodeableConceptĵ, integerĵ</t>
   </si>
   <si>
-    <t>mii-pr-icu-score-cam-icu</t>
-  </si>
-  <si>
-    <t>MII PR ICU Score CAM-ICU</t>
-  </si>
-  <si>
-    <t>null#99844-5, null#450740000</t>
+    <t>mii-pr-icu-score-faces-pain-scale-revised</t>
+  </si>
+  <si>
+    <t>MII PR ICU Score Faces Pain Scale Revised</t>
+  </si>
+  <si>
+    <t>null#1284909003</t>
+  </si>
+  <si>
+    <t>mii-pr-icu-score-gcs</t>
+  </si>
+  <si>
+    <t>MII PR ICU Score GCS</t>
+  </si>
+  <si>
+    <t>null#9269-2, null#248241002, null#153728</t>
   </si>
   <si>
     <t>CodeableConceptĵ</t>
   </si>
   <si>
-    <t>mii-pr-icu-score-faces-pain-scale-revised</t>
-  </si>
-  <si>
-    <t>MII PR ICU Score Faces Pain Scale Revised</t>
-  </si>
-  <si>
-    <t>null#1284909003</t>
-  </si>
-  <si>
-    <t>mii-pr-icu-score-gcs</t>
-  </si>
-  <si>
-    <t>MII PR ICU Score GCS</t>
-  </si>
-  <si>
-    <t>null#9269-2, null#248241002, null#153728</t>
-  </si>
-  <si>
     <t>LOINC#9267-6</t>
   </si>
   <si>
@@ -500,54 +425,18 @@
     <t>LOINC#9270-0</t>
   </si>
   <si>
-    <t>mii-pr-icu-score-icdsc</t>
-  </si>
-  <si>
-    <t>MII PR ICU Score ICDSC</t>
-  </si>
-  <si>
-    <t>null#1351995008</t>
+    <t>mii-pr-icu-score-numerische-ratingskala</t>
+  </si>
+  <si>
+    <t>MII PR ICU Score Numerische Ratingskala</t>
+  </si>
+  <si>
+    <t>null#1284857008</t>
   </si>
   <si>
     <t>integerĵ</t>
   </si>
   <si>
-    <t>mii-pr-icu-score-numerische-ratingskala</t>
-  </si>
-  <si>
-    <t>MII PR ICU Score Numerische Ratingskala</t>
-  </si>
-  <si>
-    <t>null#1284857008</t>
-  </si>
-  <si>
-    <t>mii-pr-icu-score-sofa</t>
-  </si>
-  <si>
-    <t>MII PR ICU Score SOFA</t>
-  </si>
-  <si>
-    <t>null#96789-3, null#1187491009</t>
-  </si>
-  <si>
-    <t>LOINC#96823-0, SNOMED CT#xxxx</t>
-  </si>
-  <si>
-    <t>LOINC#96826-3, SNOMED CT#xxx</t>
-  </si>
-  <si>
-    <t>LOINC#96825-5, SNOMED CT#xxx</t>
-  </si>
-  <si>
-    <t>LOINC#96824-8, SNOMED CT#xxx</t>
-  </si>
-  <si>
-    <t>LOINC#96828-9, SNOMED CT#xxx</t>
-  </si>
-  <si>
-    <t>LOINC#96827-1, SNOMED CT#xxxx</t>
-  </si>
-  <si>
     <t>mii-pr-icu-score-visuelle-analogskala</t>
   </si>
   <si>
@@ -557,30 +446,6 @@
     <t>null#38214-3, null#443394008</t>
   </si>
   <si>
-    <t>mii-pr-icu-score-wong-baker-faces-schmerzskala</t>
-  </si>
-  <si>
-    <t>MII PR ICU Score Wong-Baker-FACES-Schmerzskala</t>
-  </si>
-  <si>
-    <t>Observation Category Codes#survey</t>
-  </si>
-  <si>
-    <t>null#38221-8, null#718581005</t>
-  </si>
-  <si>
-    <t>dateTimeĵ</t>
-  </si>
-  <si>
-    <t>mii-pr-icu-score-zopa</t>
-  </si>
-  <si>
-    <t>MII PR ICU Score ZOPA</t>
-  </si>
-  <si>
-    <t>null#DGAI-ZOPA</t>
-  </si>
-  <si>
     <t>mii-pr-icu-vent-atemwegsdruck-mittlerem-expiratorischem-gasfluss</t>
   </si>
   <si>
@@ -698,15 +563,6 @@
     <t>null#250819002, null#76334-2, null#16929632</t>
   </si>
   <si>
-    <t>mii-pr-icu-vent-einstellung-inspirationsdruck</t>
-  </si>
-  <si>
-    <t>MII PR ICU Einstellung Inspirationsdruck</t>
-  </si>
-  <si>
-    <t>null#76003-3, null#151972</t>
-  </si>
-  <si>
     <t>mii-pr-icu-vent-endexpiratorischer-kohlendioxidpartialdruck</t>
   </si>
   <si>
@@ -771,18 +627,6 @@
   </si>
   <si>
     <t>null#76531-3, null#151957</t>
-  </si>
-  <si>
-    <t>mii-pr-icu-vent-maximaler-inspiratorischer-beatmungsdruck</t>
-  </si>
-  <si>
-    <t>MII PR ICU Maximaler Inspiratorischer Beatmungsdruck</t>
-  </si>
-  <si>
-    <t>null#27913002, null#151973</t>
-  </si>
-  <si>
-    <t>https://www.medizininformatik-initiative.de/fhir/ext/modul-icu/ValueSet/mii-vs-icu-code-observation-beatmung-loinc (required)</t>
   </si>
   <si>
     <t>mii-pr-icu-vent-mechanische-atemfrequenz-beatmet</t>
@@ -1015,7 +859,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:K106"/>
+  <dimension ref="A1:K74"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -1586,19 +1430,19 @@
         <v>63</v>
       </c>
       <c r="C17" t="s" s="2">
-        <v>13</v>
+        <v>64</v>
       </c>
       <c r="D17" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E17" t="s" s="2">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F17" t="s" s="2">
         <v>16</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>65</v>
+        <v>17</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>18</v>
@@ -1621,7 +1465,7 @@
         <v>67</v>
       </c>
       <c r="C18" t="s" s="2">
-        <v>13</v>
+        <v>64</v>
       </c>
       <c r="D18" t="s" s="2">
         <v>14</v>
@@ -1656,7 +1500,7 @@
         <v>70</v>
       </c>
       <c r="C19" t="s" s="2">
-        <v>13</v>
+        <v>64</v>
       </c>
       <c r="D19" t="s" s="2">
         <v>14</v>
@@ -1691,7 +1535,7 @@
         <v>73</v>
       </c>
       <c r="C20" t="s" s="2">
-        <v>13</v>
+        <v>64</v>
       </c>
       <c r="D20" t="s" s="2">
         <v>14</v>
@@ -1726,7 +1570,7 @@
         <v>76</v>
       </c>
       <c r="C21" t="s" s="2">
-        <v>13</v>
+        <v>64</v>
       </c>
       <c r="D21" t="s" s="2">
         <v>14</v>
@@ -1761,7 +1605,7 @@
         <v>79</v>
       </c>
       <c r="C22" t="s" s="2">
-        <v>13</v>
+        <v>64</v>
       </c>
       <c r="D22" t="s" s="2">
         <v>14</v>
@@ -1796,13 +1640,13 @@
         <v>82</v>
       </c>
       <c r="C23" t="s" s="2">
+        <v>64</v>
+      </c>
+      <c r="D23" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E23" t="s" s="2">
         <v>83</v>
-      </c>
-      <c r="D23" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E23" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="F23" t="s" s="2">
         <v>16</v>
@@ -1825,19 +1669,19 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="B24" t="s" s="2">
         <v>85</v>
       </c>
-      <c r="B24" t="s" s="2">
+      <c r="C24" t="s" s="2">
+        <v>64</v>
+      </c>
+      <c r="D24" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E24" t="s" s="2">
         <v>86</v>
-      </c>
-      <c r="C24" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="D24" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E24" t="s" s="2">
-        <v>87</v>
       </c>
       <c r="F24" t="s" s="2">
         <v>16</v>
@@ -1860,19 +1704,19 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="B25" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="B25" t="s" s="2">
+      <c r="C25" t="s" s="2">
+        <v>64</v>
+      </c>
+      <c r="D25" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E25" t="s" s="2">
         <v>89</v>
-      </c>
-      <c r="C25" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="D25" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E25" t="s" s="2">
-        <v>90</v>
       </c>
       <c r="F25" t="s" s="2">
         <v>16</v>
@@ -1895,13 +1739,13 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="B26" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="B26" t="s" s="2">
+      <c r="C26" t="s" s="2">
         <v>92</v>
-      </c>
-      <c r="C26" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="D26" t="s" s="2">
         <v>14</v>
@@ -1910,16 +1754,16 @@
         <v>93</v>
       </c>
       <c r="F26" t="s" s="2">
-        <v>16</v>
+        <v>94</v>
       </c>
       <c r="G26" t="s" s="2">
         <v>17</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="I26" t="s" s="2">
-        <v>19</v>
+        <v>95</v>
       </c>
       <c r="J26" t="s" s="2">
         <v>14</v>
@@ -1930,13 +1774,13 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>94</v>
+        <v>14</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="C27" t="s" s="2">
-        <v>83</v>
+        <v>14</v>
       </c>
       <c r="D27" t="s" s="2">
         <v>14</v>
@@ -1945,10 +1789,10 @@
         <v>96</v>
       </c>
       <c r="F27" t="s" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>18</v>
@@ -1965,25 +1809,25 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="B28" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="C28" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="D28" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E28" t="s" s="2">
         <v>97</v>
       </c>
-      <c r="B28" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="C28" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="D28" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E28" t="s" s="2">
-        <v>99</v>
-      </c>
       <c r="F28" t="s" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>18</v>
@@ -2000,25 +1844,25 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>100</v>
+        <v>14</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="C29" t="s" s="2">
-        <v>83</v>
+        <v>14</v>
       </c>
       <c r="D29" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E29" t="s" s="2">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="F29" t="s" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>18</v>
@@ -2035,22 +1879,22 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="C30" t="s" s="2">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="D30" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E30" t="s" s="2">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="F30" t="s" s="2">
-        <v>16</v>
+        <v>94</v>
       </c>
       <c r="G30" t="s" s="2">
         <v>17</v>
@@ -2070,22 +1914,22 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C31" t="s" s="2">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="D31" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E31" t="s" s="2">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="F31" t="s" s="2">
-        <v>16</v>
+        <v>94</v>
       </c>
       <c r="G31" t="s" s="2">
         <v>17</v>
@@ -2105,31 +1949,31 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="B32" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="C32" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="D32" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E32" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="F32" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="G32" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="H32" t="s" s="2">
         <v>109</v>
       </c>
-      <c r="B32" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="C32" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="D32" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E32" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="F32" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="G32" t="s" s="2">
-        <v>17</v>
-      </c>
-      <c r="H32" t="s" s="2">
-        <v>14</v>
-      </c>
       <c r="I32" t="s" s="2">
-        <v>114</v>
+        <v>19</v>
       </c>
       <c r="J32" t="s" s="2">
         <v>14</v>
@@ -2140,28 +1984,28 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>14</v>
+        <v>110</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C33" t="s" s="2">
-        <v>14</v>
+        <v>107</v>
       </c>
       <c r="D33" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E33" t="s" s="2">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="F33" t="s" s="2">
-        <v>14</v>
+        <v>94</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>18</v>
+        <v>109</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>19</v>
@@ -2175,25 +2019,25 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>14</v>
+        <v>113</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="C34" t="s" s="2">
-        <v>14</v>
+        <v>92</v>
       </c>
       <c r="D34" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E34" t="s" s="2">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F34" t="s" s="2">
-        <v>14</v>
+        <v>94</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>18</v>
@@ -2210,34 +2054,34 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>14</v>
+        <v>116</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="C35" t="s" s="2">
-        <v>14</v>
+        <v>118</v>
       </c>
       <c r="D35" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E35" t="s" s="2">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="F35" t="s" s="2">
-        <v>14</v>
+        <v>94</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>18</v>
+        <v>109</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>19</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>14</v>
+        <v>120</v>
       </c>
       <c r="K35" t="s" s="2">
         <v>14</v>
@@ -2245,22 +2089,22 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="C36" t="s" s="2">
-        <v>111</v>
+        <v>64</v>
       </c>
       <c r="D36" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E36" t="s" s="2">
-        <v>120</v>
+        <v>15</v>
       </c>
       <c r="F36" t="s" s="2">
-        <v>113</v>
+        <v>16</v>
       </c>
       <c r="G36" t="s" s="2">
         <v>17</v>
@@ -2280,28 +2124,28 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C37" t="s" s="2">
-        <v>111</v>
+        <v>125</v>
       </c>
       <c r="D37" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E37" t="s" s="2">
-        <v>123</v>
+        <v>14</v>
       </c>
       <c r="F37" t="s" s="2">
-        <v>113</v>
+        <v>16</v>
       </c>
       <c r="G37" t="s" s="2">
         <v>17</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>18</v>
+        <v>126</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>19</v>
@@ -2315,28 +2159,28 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="B38" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="C38" t="s" s="2">
         <v>125</v>
       </c>
-      <c r="C38" t="s" s="2">
-        <v>126</v>
-      </c>
       <c r="D38" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E38" t="s" s="2">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="F38" t="s" s="2">
-        <v>113</v>
+        <v>16</v>
       </c>
       <c r="G38" t="s" s="2">
         <v>17</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>128</v>
+        <v>18</v>
       </c>
       <c r="I38" t="s" s="2">
         <v>19</v>
@@ -2350,28 +2194,28 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C39" t="s" s="2">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D39" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E39" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F39" t="s" s="2">
-        <v>113</v>
+        <v>16</v>
       </c>
       <c r="G39" t="s" s="2">
         <v>17</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>128</v>
+        <v>18</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>19</v>
@@ -2385,124 +2229,124 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>132</v>
+        <v>14</v>
       </c>
       <c r="B40" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="C40" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="D40" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E40" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="F40" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="G40" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="H40" t="s" s="2">
         <v>133</v>
       </c>
-      <c r="C40" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="D40" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E40" t="s" s="2">
+      <c r="I40" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J40" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K40" t="s" s="2">
         <v>134</v>
-      </c>
-      <c r="F40" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="G40" t="s" s="2">
-        <v>17</v>
-      </c>
-      <c r="H40" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="I40" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="J40" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="K40" t="s" s="2">
-        <v>14</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="B41" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="C41" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="D41" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E41" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="F41" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="G41" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="H41" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="I41" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J41" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K41" t="s" s="2">
         <v>135</v>
-      </c>
-      <c r="B41" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="C41" t="s" s="2">
-        <v>126</v>
-      </c>
-      <c r="D41" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E41" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="F41" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="G41" t="s" s="2">
-        <v>17</v>
-      </c>
-      <c r="H41" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="I41" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="J41" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="K41" t="s" s="2">
-        <v>14</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>138</v>
+        <v>14</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="C42" t="s" s="2">
-        <v>140</v>
+        <v>14</v>
       </c>
       <c r="D42" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E42" t="s" s="2">
-        <v>141</v>
+        <v>14</v>
       </c>
       <c r="F42" t="s" s="2">
-        <v>113</v>
+        <v>14</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="I42" t="s" s="2">
         <v>19</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>142</v>
+        <v>14</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>14</v>
+        <v>136</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="C43" t="s" s="2">
-        <v>83</v>
+        <v>125</v>
       </c>
       <c r="D43" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E43" t="s" s="2">
-        <v>15</v>
+        <v>139</v>
       </c>
       <c r="F43" t="s" s="2">
         <v>16</v>
@@ -2511,7 +2355,7 @@
         <v>17</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>18</v>
+        <v>140</v>
       </c>
       <c r="I43" t="s" s="2">
         <v>19</v>
@@ -2525,19 +2369,19 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="C44" t="s" s="2">
-        <v>147</v>
+        <v>125</v>
       </c>
       <c r="D44" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E44" t="s" s="2">
-        <v>14</v>
+        <v>143</v>
       </c>
       <c r="F44" t="s" s="2">
         <v>16</v>
@@ -2546,7 +2390,7 @@
         <v>17</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>148</v>
+        <v>18</v>
       </c>
       <c r="I44" t="s" s="2">
         <v>19</v>
@@ -2560,28 +2404,28 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="C45" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="D45" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E45" t="s" s="2">
         <v>147</v>
       </c>
-      <c r="D45" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E45" t="s" s="2">
-        <v>151</v>
-      </c>
       <c r="F45" t="s" s="2">
-        <v>16</v>
+        <v>148</v>
       </c>
       <c r="G45" t="s" s="2">
         <v>17</v>
       </c>
       <c r="H45" t="s" s="2">
-        <v>152</v>
+        <v>18</v>
       </c>
       <c r="I45" t="s" s="2">
         <v>19</v>
@@ -2595,28 +2439,28 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>14</v>
+        <v>149</v>
       </c>
       <c r="B46" t="s" s="2">
         <v>150</v>
       </c>
       <c r="C46" t="s" s="2">
-        <v>14</v>
+        <v>146</v>
       </c>
       <c r="D46" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E46" t="s" s="2">
-        <v>14</v>
+        <v>151</v>
       </c>
       <c r="F46" t="s" s="2">
-        <v>14</v>
+        <v>148</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>152</v>
+        <v>18</v>
       </c>
       <c r="I46" t="s" s="2">
         <v>19</v>
@@ -2630,28 +2474,28 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>14</v>
+        <v>152</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="C47" t="s" s="2">
-        <v>14</v>
+        <v>146</v>
       </c>
       <c r="D47" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E47" t="s" s="2">
-        <v>14</v>
+        <v>154</v>
       </c>
       <c r="F47" t="s" s="2">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>152</v>
+        <v>18</v>
       </c>
       <c r="I47" t="s" s="2">
         <v>19</v>
@@ -2665,28 +2509,28 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>14</v>
+        <v>155</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="C48" t="s" s="2">
-        <v>14</v>
+        <v>146</v>
       </c>
       <c r="D48" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E48" t="s" s="2">
-        <v>14</v>
+        <v>157</v>
       </c>
       <c r="F48" t="s" s="2">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H48" t="s" s="2">
-        <v>152</v>
+        <v>18</v>
       </c>
       <c r="I48" t="s" s="2">
         <v>19</v>
@@ -2700,28 +2544,28 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>14</v>
+        <v>158</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="C49" t="s" s="2">
-        <v>14</v>
+        <v>146</v>
       </c>
       <c r="D49" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E49" t="s" s="2">
-        <v>14</v>
+        <v>160</v>
       </c>
       <c r="F49" t="s" s="2">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H49" t="s" s="2">
-        <v>152</v>
+        <v>18</v>
       </c>
       <c r="I49" t="s" s="2">
         <v>19</v>
@@ -2735,22 +2579,22 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="C50" t="s" s="2">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D50" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E50" t="s" s="2">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="F50" t="s" s="2">
-        <v>16</v>
+        <v>164</v>
       </c>
       <c r="G50" t="s" s="2">
         <v>17</v>
@@ -2770,22 +2614,22 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>156</v>
+        <v>165</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="C51" t="s" s="2">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D51" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E51" t="s" s="2">
-        <v>158</v>
+        <v>167</v>
       </c>
       <c r="F51" t="s" s="2">
-        <v>16</v>
+        <v>164</v>
       </c>
       <c r="G51" t="s" s="2">
         <v>17</v>
@@ -2805,28 +2649,28 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>14</v>
+        <v>168</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="C52" t="s" s="2">
-        <v>14</v>
+        <v>146</v>
       </c>
       <c r="D52" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E52" t="s" s="2">
-        <v>14</v>
+        <v>170</v>
       </c>
       <c r="F52" t="s" s="2">
-        <v>14</v>
+        <v>164</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H52" t="s" s="2">
-        <v>152</v>
+        <v>18</v>
       </c>
       <c r="I52" t="s" s="2">
         <v>19</v>
@@ -2835,33 +2679,33 @@
         <v>14</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>159</v>
+        <v>14</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>14</v>
+        <v>171</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="C53" t="s" s="2">
-        <v>14</v>
+        <v>146</v>
       </c>
       <c r="D53" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E53" t="s" s="2">
-        <v>14</v>
+        <v>173</v>
       </c>
       <c r="F53" t="s" s="2">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H53" t="s" s="2">
-        <v>152</v>
+        <v>18</v>
       </c>
       <c r="I53" t="s" s="2">
         <v>19</v>
@@ -2870,33 +2714,33 @@
         <v>14</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>160</v>
+        <v>14</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>14</v>
+        <v>174</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>157</v>
+        <v>175</v>
       </c>
       <c r="C54" t="s" s="2">
-        <v>14</v>
+        <v>146</v>
       </c>
       <c r="D54" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E54" t="s" s="2">
-        <v>14</v>
+        <v>176</v>
       </c>
       <c r="F54" t="s" s="2">
-        <v>14</v>
+        <v>148</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H54" t="s" s="2">
-        <v>152</v>
+        <v>18</v>
       </c>
       <c r="I54" t="s" s="2">
         <v>19</v>
@@ -2905,33 +2749,33 @@
         <v>14</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>161</v>
+        <v>14</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>162</v>
+        <v>177</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>163</v>
+        <v>178</v>
       </c>
       <c r="C55" t="s" s="2">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D55" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E55" t="s" s="2">
-        <v>164</v>
+        <v>179</v>
       </c>
       <c r="F55" t="s" s="2">
-        <v>16</v>
+        <v>148</v>
       </c>
       <c r="G55" t="s" s="2">
         <v>17</v>
       </c>
       <c r="H55" t="s" s="2">
-        <v>165</v>
+        <v>18</v>
       </c>
       <c r="I55" t="s" s="2">
         <v>19</v>
@@ -2945,28 +2789,28 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>14</v>
+        <v>180</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>163</v>
+        <v>181</v>
       </c>
       <c r="C56" t="s" s="2">
-        <v>14</v>
+        <v>146</v>
       </c>
       <c r="D56" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E56" t="s" s="2">
-        <v>14</v>
+        <v>182</v>
       </c>
       <c r="F56" t="s" s="2">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H56" t="s" s="2">
-        <v>165</v>
+        <v>18</v>
       </c>
       <c r="I56" t="s" s="2">
         <v>19</v>
@@ -2980,28 +2824,28 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>14</v>
+        <v>183</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>163</v>
+        <v>184</v>
       </c>
       <c r="C57" t="s" s="2">
-        <v>14</v>
+        <v>185</v>
       </c>
       <c r="D57" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E57" t="s" s="2">
-        <v>14</v>
+        <v>186</v>
       </c>
       <c r="F57" t="s" s="2">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H57" t="s" s="2">
-        <v>165</v>
+        <v>18</v>
       </c>
       <c r="I57" t="s" s="2">
         <v>19</v>
@@ -3015,28 +2859,28 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>14</v>
+        <v>187</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>163</v>
+        <v>188</v>
       </c>
       <c r="C58" t="s" s="2">
-        <v>14</v>
+        <v>146</v>
       </c>
       <c r="D58" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E58" t="s" s="2">
-        <v>14</v>
+        <v>189</v>
       </c>
       <c r="F58" t="s" s="2">
-        <v>14</v>
+        <v>164</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H58" t="s" s="2">
-        <v>165</v>
+        <v>18</v>
       </c>
       <c r="I58" t="s" s="2">
         <v>19</v>
@@ -3050,28 +2894,28 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>14</v>
+        <v>190</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>163</v>
+        <v>191</v>
       </c>
       <c r="C59" t="s" s="2">
-        <v>14</v>
+        <v>185</v>
       </c>
       <c r="D59" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E59" t="s" s="2">
-        <v>14</v>
+        <v>192</v>
       </c>
       <c r="F59" t="s" s="2">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H59" t="s" s="2">
-        <v>165</v>
+        <v>18</v>
       </c>
       <c r="I59" t="s" s="2">
         <v>19</v>
@@ -3085,28 +2929,28 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>14</v>
+        <v>193</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>163</v>
+        <v>194</v>
       </c>
       <c r="C60" t="s" s="2">
-        <v>14</v>
+        <v>185</v>
       </c>
       <c r="D60" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E60" t="s" s="2">
-        <v>14</v>
+        <v>195</v>
       </c>
       <c r="F60" t="s" s="2">
-        <v>14</v>
+        <v>164</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H60" t="s" s="2">
-        <v>165</v>
+        <v>18</v>
       </c>
       <c r="I60" t="s" s="2">
         <v>19</v>
@@ -3120,28 +2964,28 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>14</v>
+        <v>196</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>163</v>
+        <v>197</v>
       </c>
       <c r="C61" t="s" s="2">
-        <v>14</v>
+        <v>185</v>
       </c>
       <c r="D61" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E61" t="s" s="2">
-        <v>14</v>
+        <v>198</v>
       </c>
       <c r="F61" t="s" s="2">
-        <v>14</v>
+        <v>148</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H61" t="s" s="2">
-        <v>165</v>
+        <v>18</v>
       </c>
       <c r="I61" t="s" s="2">
         <v>19</v>
@@ -3155,28 +2999,28 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>14</v>
+        <v>199</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>163</v>
+        <v>200</v>
       </c>
       <c r="C62" t="s" s="2">
-        <v>14</v>
+        <v>146</v>
       </c>
       <c r="D62" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E62" t="s" s="2">
-        <v>14</v>
+        <v>201</v>
       </c>
       <c r="F62" t="s" s="2">
-        <v>14</v>
+        <v>164</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H62" t="s" s="2">
-        <v>165</v>
+        <v>18</v>
       </c>
       <c r="I62" t="s" s="2">
         <v>19</v>
@@ -3190,28 +3034,28 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>14</v>
+        <v>202</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>163</v>
+        <v>203</v>
       </c>
       <c r="C63" t="s" s="2">
-        <v>14</v>
+        <v>146</v>
       </c>
       <c r="D63" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E63" t="s" s="2">
-        <v>14</v>
+        <v>204</v>
       </c>
       <c r="F63" t="s" s="2">
-        <v>14</v>
+        <v>164</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H63" t="s" s="2">
-        <v>165</v>
+        <v>18</v>
       </c>
       <c r="I63" t="s" s="2">
         <v>19</v>
@@ -3225,19 +3069,19 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>166</v>
+        <v>205</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>167</v>
+        <v>206</v>
       </c>
       <c r="C64" t="s" s="2">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D64" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E64" t="s" s="2">
-        <v>168</v>
+        <v>207</v>
       </c>
       <c r="F64" t="s" s="2">
         <v>16</v>
@@ -3246,7 +3090,7 @@
         <v>17</v>
       </c>
       <c r="H64" t="s" s="2">
-        <v>165</v>
+        <v>18</v>
       </c>
       <c r="I64" t="s" s="2">
         <v>19</v>
@@ -3260,19 +3104,19 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>169</v>
+        <v>208</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>170</v>
+        <v>209</v>
       </c>
       <c r="C65" t="s" s="2">
-        <v>147</v>
+        <v>14</v>
       </c>
       <c r="D65" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E65" t="s" s="2">
-        <v>171</v>
+        <v>210</v>
       </c>
       <c r="F65" t="s" s="2">
         <v>16</v>
@@ -3281,7 +3125,7 @@
         <v>17</v>
       </c>
       <c r="H65" t="s" s="2">
-        <v>165</v>
+        <v>18</v>
       </c>
       <c r="I65" t="s" s="2">
         <v>19</v>
@@ -3295,28 +3139,28 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>14</v>
+        <v>211</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>170</v>
+        <v>212</v>
       </c>
       <c r="C66" t="s" s="2">
-        <v>14</v>
+        <v>146</v>
       </c>
       <c r="D66" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E66" t="s" s="2">
-        <v>172</v>
+        <v>213</v>
       </c>
       <c r="F66" t="s" s="2">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H66" t="s" s="2">
-        <v>165</v>
+        <v>18</v>
       </c>
       <c r="I66" t="s" s="2">
         <v>19</v>
@@ -3330,28 +3174,28 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>14</v>
+        <v>214</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>170</v>
+        <v>215</v>
       </c>
       <c r="C67" t="s" s="2">
-        <v>14</v>
+        <v>146</v>
       </c>
       <c r="D67" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E67" t="s" s="2">
-        <v>173</v>
+        <v>216</v>
       </c>
       <c r="F67" t="s" s="2">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H67" t="s" s="2">
-        <v>165</v>
+        <v>18</v>
       </c>
       <c r="I67" t="s" s="2">
         <v>19</v>
@@ -3365,28 +3209,28 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>14</v>
+        <v>217</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>170</v>
+        <v>218</v>
       </c>
       <c r="C68" t="s" s="2">
-        <v>14</v>
+        <v>146</v>
       </c>
       <c r="D68" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E68" t="s" s="2">
-        <v>174</v>
+        <v>219</v>
       </c>
       <c r="F68" t="s" s="2">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H68" t="s" s="2">
-        <v>165</v>
+        <v>18</v>
       </c>
       <c r="I68" t="s" s="2">
         <v>19</v>
@@ -3400,28 +3244,28 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>14</v>
+        <v>220</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>170</v>
+        <v>221</v>
       </c>
       <c r="C69" t="s" s="2">
-        <v>14</v>
+        <v>146</v>
       </c>
       <c r="D69" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E69" t="s" s="2">
-        <v>175</v>
+        <v>222</v>
       </c>
       <c r="F69" t="s" s="2">
-        <v>14</v>
+        <v>164</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H69" t="s" s="2">
-        <v>165</v>
+        <v>18</v>
       </c>
       <c r="I69" t="s" s="2">
         <v>19</v>
@@ -3435,28 +3279,28 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>14</v>
+        <v>223</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>170</v>
+        <v>224</v>
       </c>
       <c r="C70" t="s" s="2">
-        <v>14</v>
+        <v>146</v>
       </c>
       <c r="D70" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E70" t="s" s="2">
-        <v>176</v>
+        <v>225</v>
       </c>
       <c r="F70" t="s" s="2">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H70" t="s" s="2">
-        <v>165</v>
+        <v>18</v>
       </c>
       <c r="I70" t="s" s="2">
         <v>19</v>
@@ -3470,28 +3314,28 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>14</v>
+        <v>226</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>170</v>
+        <v>227</v>
       </c>
       <c r="C71" t="s" s="2">
-        <v>14</v>
+        <v>146</v>
       </c>
       <c r="D71" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E71" t="s" s="2">
-        <v>177</v>
+        <v>228</v>
       </c>
       <c r="F71" t="s" s="2">
-        <v>14</v>
+        <v>148</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H71" t="s" s="2">
-        <v>165</v>
+        <v>18</v>
       </c>
       <c r="I71" t="s" s="2">
         <v>19</v>
@@ -3505,22 +3349,22 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>178</v>
+        <v>229</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>179</v>
+        <v>230</v>
       </c>
       <c r="C72" t="s" s="2">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D72" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E72" t="s" s="2">
-        <v>180</v>
+        <v>231</v>
       </c>
       <c r="F72" t="s" s="2">
-        <v>16</v>
+        <v>148</v>
       </c>
       <c r="G72" t="s" s="2">
         <v>17</v>
@@ -3540,25 +3384,25 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>181</v>
+        <v>232</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>182</v>
+        <v>233</v>
       </c>
       <c r="C73" t="s" s="2">
-        <v>183</v>
+        <v>146</v>
       </c>
       <c r="D73" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E73" t="s" s="2">
-        <v>184</v>
+        <v>234</v>
       </c>
       <c r="F73" t="s" s="2">
-        <v>16</v>
+        <v>148</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>185</v>
+        <v>17</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>18</v>
@@ -3575,19 +3419,19 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>186</v>
+        <v>235</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>187</v>
+        <v>236</v>
       </c>
       <c r="C74" t="s" s="2">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D74" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E74" t="s" s="2">
-        <v>188</v>
+        <v>237</v>
       </c>
       <c r="F74" t="s" s="2">
         <v>16</v>
@@ -3596,7 +3440,7 @@
         <v>17</v>
       </c>
       <c r="H74" t="s" s="2">
-        <v>152</v>
+        <v>18</v>
       </c>
       <c r="I74" t="s" s="2">
         <v>19</v>
@@ -3605,1126 +3449,6 @@
         <v>14</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="B75" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="C75" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="D75" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E75" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="F75" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="G75" t="s" s="2">
-        <v>17</v>
-      </c>
-      <c r="H75" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="I75" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="J75" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="K75" t="s" s="2">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="s" s="2">
-        <v>194</v>
-      </c>
-      <c r="B76" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="C76" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="D76" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E76" t="s" s="2">
-        <v>196</v>
-      </c>
-      <c r="F76" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="G76" t="s" s="2">
-        <v>17</v>
-      </c>
-      <c r="H76" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="I76" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="J76" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="K76" t="s" s="2">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="B77" t="s" s="2">
-        <v>198</v>
-      </c>
-      <c r="C77" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="D77" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E77" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="F77" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="G77" t="s" s="2">
-        <v>17</v>
-      </c>
-      <c r="H77" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="I77" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="J77" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="K77" t="s" s="2">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="B78" t="s" s="2">
-        <v>201</v>
-      </c>
-      <c r="C78" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="D78" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E78" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="F78" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="G78" t="s" s="2">
-        <v>17</v>
-      </c>
-      <c r="H78" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="I78" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="J78" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="K78" t="s" s="2">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="B79" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="C79" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="D79" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E79" t="s" s="2">
-        <v>205</v>
-      </c>
-      <c r="F79" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="G79" t="s" s="2">
-        <v>17</v>
-      </c>
-      <c r="H79" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="I79" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="J79" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="K79" t="s" s="2">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="B80" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="C80" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="D80" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E80" t="s" s="2">
-        <v>208</v>
-      </c>
-      <c r="F80" t="s" s="2">
-        <v>209</v>
-      </c>
-      <c r="G80" t="s" s="2">
-        <v>17</v>
-      </c>
-      <c r="H80" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="I80" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="J80" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="K80" t="s" s="2">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="B81" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="C81" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="D81" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E81" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="F81" t="s" s="2">
-        <v>209</v>
-      </c>
-      <c r="G81" t="s" s="2">
-        <v>17</v>
-      </c>
-      <c r="H81" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="I81" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="J81" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="K81" t="s" s="2">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="B82" t="s" s="2">
-        <v>214</v>
-      </c>
-      <c r="C82" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="D82" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E82" t="s" s="2">
-        <v>215</v>
-      </c>
-      <c r="F82" t="s" s="2">
-        <v>209</v>
-      </c>
-      <c r="G82" t="s" s="2">
-        <v>17</v>
-      </c>
-      <c r="H82" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="I82" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="J82" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="K82" t="s" s="2">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="B83" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="C83" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="D83" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E83" t="s" s="2">
-        <v>218</v>
-      </c>
-      <c r="F83" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="G83" t="s" s="2">
-        <v>17</v>
-      </c>
-      <c r="H83" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="I83" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="J83" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="K83" t="s" s="2">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="B84" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="C84" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="D84" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E84" t="s" s="2">
-        <v>221</v>
-      </c>
-      <c r="F84" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="G84" t="s" s="2">
-        <v>17</v>
-      </c>
-      <c r="H84" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="I84" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="J84" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="K84" t="s" s="2">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="B85" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="C85" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="D85" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E85" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="F85" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="G85" t="s" s="2">
-        <v>17</v>
-      </c>
-      <c r="H85" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="I85" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="J85" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="K85" t="s" s="2">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="B86" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="C86" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="D86" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E86" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="F86" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="G86" t="s" s="2">
-        <v>17</v>
-      </c>
-      <c r="H86" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="I86" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="J86" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="K86" t="s" s="2">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="B87" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="C87" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="D87" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E87" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="F87" t="s" s="2">
-        <v>209</v>
-      </c>
-      <c r="G87" t="s" s="2">
-        <v>17</v>
-      </c>
-      <c r="H87" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="I87" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="J87" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="K87" t="s" s="2">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="s" s="2">
-        <v>231</v>
-      </c>
-      <c r="B88" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="C88" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="D88" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E88" t="s" s="2">
-        <v>234</v>
-      </c>
-      <c r="F88" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="G88" t="s" s="2">
-        <v>17</v>
-      </c>
-      <c r="H88" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="I88" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="J88" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="K88" t="s" s="2">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="s" s="2">
-        <v>235</v>
-      </c>
-      <c r="B89" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="C89" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="D89" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E89" t="s" s="2">
-        <v>237</v>
-      </c>
-      <c r="F89" t="s" s="2">
-        <v>209</v>
-      </c>
-      <c r="G89" t="s" s="2">
-        <v>17</v>
-      </c>
-      <c r="H89" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="I89" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="J89" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="K89" t="s" s="2">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="s" s="2">
-        <v>238</v>
-      </c>
-      <c r="B90" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="C90" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="D90" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E90" t="s" s="2">
-        <v>240</v>
-      </c>
-      <c r="F90" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="G90" t="s" s="2">
-        <v>17</v>
-      </c>
-      <c r="H90" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="I90" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="J90" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="K90" t="s" s="2">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="B91" t="s" s="2">
-        <v>242</v>
-      </c>
-      <c r="C91" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="D91" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E91" t="s" s="2">
-        <v>243</v>
-      </c>
-      <c r="F91" t="s" s="2">
-        <v>209</v>
-      </c>
-      <c r="G91" t="s" s="2">
-        <v>17</v>
-      </c>
-      <c r="H91" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="I91" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="J91" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="K91" t="s" s="2">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="s" s="2">
-        <v>244</v>
-      </c>
-      <c r="B92" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="C92" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="D92" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E92" t="s" s="2">
-        <v>246</v>
-      </c>
-      <c r="F92" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="G92" t="s" s="2">
-        <v>17</v>
-      </c>
-      <c r="H92" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="I92" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="J92" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="K92" t="s" s="2">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="B93" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="C93" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="D93" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E93" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="F93" t="s" s="2">
-        <v>209</v>
-      </c>
-      <c r="G93" t="s" s="2">
-        <v>17</v>
-      </c>
-      <c r="H93" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="I93" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="J93" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="K93" t="s" s="2">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="s" s="2">
-        <v>250</v>
-      </c>
-      <c r="B94" t="s" s="2">
-        <v>251</v>
-      </c>
-      <c r="C94" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="D94" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E94" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="F94" t="s" s="2">
-        <v>209</v>
-      </c>
-      <c r="G94" t="s" s="2">
-        <v>17</v>
-      </c>
-      <c r="H94" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="I94" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="J94" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="K94" t="s" s="2">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="s" s="2">
-        <v>253</v>
-      </c>
-      <c r="B95" t="s" s="2">
-        <v>254</v>
-      </c>
-      <c r="C95" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="D95" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E95" t="s" s="2">
-        <v>255</v>
-      </c>
-      <c r="F95" t="s" s="2">
-        <v>256</v>
-      </c>
-      <c r="G95" t="s" s="2">
-        <v>17</v>
-      </c>
-      <c r="H95" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="I95" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="J95" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="K95" t="s" s="2">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="s" s="2">
-        <v>257</v>
-      </c>
-      <c r="B96" t="s" s="2">
-        <v>258</v>
-      </c>
-      <c r="C96" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="D96" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E96" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="F96" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="G96" t="s" s="2">
-        <v>17</v>
-      </c>
-      <c r="H96" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="I96" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="J96" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="K96" t="s" s="2">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="s" s="2">
-        <v>260</v>
-      </c>
-      <c r="B97" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="C97" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="D97" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E97" t="s" s="2">
-        <v>262</v>
-      </c>
-      <c r="F97" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="G97" t="s" s="2">
-        <v>17</v>
-      </c>
-      <c r="H97" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="I97" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="J97" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="K97" t="s" s="2">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="s" s="2">
-        <v>263</v>
-      </c>
-      <c r="B98" t="s" s="2">
-        <v>264</v>
-      </c>
-      <c r="C98" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="D98" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E98" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="F98" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="G98" t="s" s="2">
-        <v>17</v>
-      </c>
-      <c r="H98" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="I98" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="J98" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="K98" t="s" s="2">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="B99" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="C99" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="D99" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E99" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="F99" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="G99" t="s" s="2">
-        <v>17</v>
-      </c>
-      <c r="H99" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="I99" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="J99" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="K99" t="s" s="2">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="s" s="2">
-        <v>269</v>
-      </c>
-      <c r="B100" t="s" s="2">
-        <v>270</v>
-      </c>
-      <c r="C100" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="D100" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E100" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="F100" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="G100" t="s" s="2">
-        <v>17</v>
-      </c>
-      <c r="H100" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="I100" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="J100" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="K100" t="s" s="2">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="B101" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="C101" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="D101" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E101" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="F101" t="s" s="2">
-        <v>209</v>
-      </c>
-      <c r="G101" t="s" s="2">
-        <v>17</v>
-      </c>
-      <c r="H101" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="I101" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="J101" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="K101" t="s" s="2">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="B102" t="s" s="2">
-        <v>276</v>
-      </c>
-      <c r="C102" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="D102" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E102" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="F102" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="G102" t="s" s="2">
-        <v>17</v>
-      </c>
-      <c r="H102" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="I102" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="J102" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="K102" t="s" s="2">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="s" s="2">
-        <v>278</v>
-      </c>
-      <c r="B103" t="s" s="2">
-        <v>279</v>
-      </c>
-      <c r="C103" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="D103" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E103" t="s" s="2">
-        <v>280</v>
-      </c>
-      <c r="F103" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="G103" t="s" s="2">
-        <v>17</v>
-      </c>
-      <c r="H103" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="I103" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="J103" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="K103" t="s" s="2">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="B104" t="s" s="2">
-        <v>282</v>
-      </c>
-      <c r="C104" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="D104" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E104" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="F104" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="G104" t="s" s="2">
-        <v>17</v>
-      </c>
-      <c r="H104" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="I104" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="J104" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="K104" t="s" s="2">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="B105" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="C105" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="D105" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E105" t="s" s="2">
-        <v>286</v>
-      </c>
-      <c r="F105" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="G105" t="s" s="2">
-        <v>17</v>
-      </c>
-      <c r="H105" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="I105" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="J105" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="K105" t="s" s="2">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="B106" t="s" s="2">
-        <v>288</v>
-      </c>
-      <c r="C106" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="D106" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E106" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="F106" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="G106" t="s" s="2">
-        <v>17</v>
-      </c>
-      <c r="H106" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="I106" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="J106" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="K106" t="s" s="2">
         <v>14</v>
       </c>
     </row>

--- a/branches/dev/observations-summary.xlsx
+++ b/branches/dev/observations-summary.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="814" uniqueCount="238">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1353" uniqueCount="347">
   <si>
     <t>Profile</t>
   </si>
@@ -173,6 +173,15 @@
     <t>null#251845003, null#9203-1, null#null</t>
   </si>
   <si>
+    <t>mii-pr-icu-bilanz-einfuhr-abgepumpte-muttermilch</t>
+  </si>
+  <si>
+    <t>MII PR ICU Bilanz Einfuhr Abgepumpte Muttermilch</t>
+  </si>
+  <si>
+    <t>null#819975003, null#null, null#null</t>
+  </si>
+  <si>
     <t>mii-pr-icu-bilanz-einfuhr-enterale-fluessigkeit</t>
   </si>
   <si>
@@ -191,6 +200,54 @@
     <t>null#251852001, null#9103-3, null#null</t>
   </si>
   <si>
+    <t>mii-pr-icu-bilanz-einfuhr-kalorien-24h</t>
+  </si>
+  <si>
+    <t>MII PR ICU Bilanz Einfuhr Kalorien 24h</t>
+  </si>
+  <si>
+    <t>null#787787004, null#9057-1, null#null</t>
+  </si>
+  <si>
+    <t>Periodĵ</t>
+  </si>
+  <si>
+    <t>mii-pr-icu-bilanz-einfuhr-muttermilch</t>
+  </si>
+  <si>
+    <t>MII PR ICU Bilanz Einfuhr Muttermilch</t>
+  </si>
+  <si>
+    <t>null#1204299001, null#null, null#null</t>
+  </si>
+  <si>
+    <t>mii-pr-icu-bilanz-einfuhr-orale-fluessigkeit</t>
+  </si>
+  <si>
+    <t>MII PR ICU Bilanz Einfuhr Orale Fluessigkeit</t>
+  </si>
+  <si>
+    <t>null#251853006, null#9000-1, null#null</t>
+  </si>
+  <si>
+    <t>mii-pr-icu-bilanz-einfuhr-saeuglingsnahrung</t>
+  </si>
+  <si>
+    <t>MII PR ICU Bilanz Einfuhr Saeuglingsnahrung</t>
+  </si>
+  <si>
+    <t>null#1204305004, null#null, null#null</t>
+  </si>
+  <si>
+    <t>mii-pr-icu-bilanz-einfuhr-spendermilch</t>
+  </si>
+  <si>
+    <t>MII PR ICU Bilanz Einfuhr Spendermilch</t>
+  </si>
+  <si>
+    <t>null#819973005, null#null, null#null</t>
+  </si>
+  <si>
     <t>mii-pr-icu-bilanz-tagesbilanz-fluessigkeit</t>
   </si>
   <si>
@@ -221,6 +278,24 @@
     <t>null#444479000, null#null, null#null</t>
   </si>
   <si>
+    <t>mii-pr-icu-ect-blutfluss-extrakorporaler-gasaustausch</t>
+  </si>
+  <si>
+    <t>MII PR ICU Blutfluss Extrakorporaler Gasaustausch</t>
+  </si>
+  <si>
+    <t>null#251288004, null#null, null#null</t>
+  </si>
+  <si>
+    <t>mii-pr-icu-ect-blutflussindex-extrakorporaler-gasaustausch</t>
+  </si>
+  <si>
+    <t>MII PR ICU Blutflussindex Extrakorporaler Gasaustausch</t>
+  </si>
+  <si>
+    <t>null#251289007, null#null, null#null</t>
+  </si>
+  <si>
     <t>mii-pr-icu-ect-dauer-extrakorporaler-gasaustausch</t>
   </si>
   <si>
@@ -257,6 +332,15 @@
     <t>null#401000124105, null#null, null#null</t>
   </si>
   <si>
+    <t>mii-pr-icu-ect-ionisiertes-kalzium-nierenersatzverfahren</t>
+  </si>
+  <si>
+    <t>MII PR ICU Ionisiertes Kalzium Nierenersatzverfahren</t>
+  </si>
+  <si>
+    <t>null#null, null#83064-6, null#null</t>
+  </si>
+  <si>
     <t>mii-pr-icu-ect-substituatfluss</t>
   </si>
   <si>
@@ -329,21 +413,60 @@
     <t>null#364075005, null#8867-4, null#147842</t>
   </si>
   <si>
+    <t>mii-pr-icu-muv-herzzeitvolumen</t>
+  </si>
+  <si>
+    <t>MII PR ICU MUV Herzzeitvolumen</t>
+  </si>
+  <si>
+    <t>Observation Category Codes#vital-signs, SNOMED CT#248326004</t>
+  </si>
+  <si>
+    <t>null#8741-1, null#82799009, null#150276</t>
+  </si>
+  <si>
+    <t>mii-pr-icu-muv-ideales-koerpergewicht</t>
+  </si>
+  <si>
+    <t>MII PR ICU MUV Ideales Koerpergewicht</t>
+  </si>
+  <si>
+    <t>null#50064-5, null#170804003, null#188796</t>
+  </si>
+  <si>
+    <t>mii-pr-icu-muv-intrakranieller-druck</t>
+  </si>
+  <si>
+    <t>MII PR ICU MUV Intrakranieller Druck (ICP)</t>
+  </si>
+  <si>
+    <t>null#60956-0, null#250844005, null#153608</t>
+  </si>
+  <si>
+    <t>SNOMED CT#731998000</t>
+  </si>
+  <si>
     <t>mii-pr-icu-muv-koerpergewicht</t>
   </si>
   <si>
     <t>MII PR ICU MUV Koerpergewicht</t>
   </si>
   <si>
-    <t>Observation Category Codes#vital-signs, SNOMED CT#248326004</t>
-  </si>
-  <si>
     <t>null#29463-7, null#8339-4, null#27113001</t>
   </si>
   <si>
     <t>Quantityĵ, CodeableConceptĵ, stringĵ, booleanĵ, integerĵ, Rangeĵ, Ratioĵ, SampledDataĵ, timeĵ, dateTimeĵ, Periodĵ</t>
   </si>
   <si>
+    <t>mii-pr-icu-muv-koerpergewicht-perzentil</t>
+  </si>
+  <si>
+    <t>MII PR ICU MUV Koerpergewicht Perzentil (altersabhaengig)</t>
+  </si>
+  <si>
+    <t>null#8336-0, null#1153592008</t>
+  </si>
+  <si>
     <t>mii-pr-icu-muv-koerpergroesse</t>
   </si>
   <si>
@@ -353,6 +476,15 @@
     <t>null#8302-2, null#89269-5, null#1153637007</t>
   </si>
   <si>
+    <t>mii-pr-icu-muv-koerpergroesse-perzentil</t>
+  </si>
+  <si>
+    <t>MII PR ICU MUV Koerpergroesse Perzentil (altersabhaengig)</t>
+  </si>
+  <si>
+    <t>null#1153605006</t>
+  </si>
+  <si>
     <t>mii-pr-icu-muv-koerperlaenge</t>
   </si>
   <si>
@@ -362,6 +494,15 @@
     <t>null#8306-3, null#1149101003</t>
   </si>
   <si>
+    <t>mii-pr-icu-muv-kohlendioxid-produktion</t>
+  </si>
+  <si>
+    <t>MII PR ICU MUV Kohlendioxid Produktion</t>
+  </si>
+  <si>
+    <t>null#60825-7, null#251408004</t>
+  </si>
+  <si>
     <t>mii-pr-icu-muv-kopfumfang</t>
   </si>
   <si>
@@ -377,6 +518,27 @@
     <t>SNOMED CT#69536005</t>
   </si>
   <si>
+    <t>mii-pr-icu-muv-pulmonalarterieller-wedge-druck</t>
+  </si>
+  <si>
+    <t>MII PR ICU MUV Pulmonalarterieller Wedge-Druck</t>
+  </si>
+  <si>
+    <t>null#75994-4, null#118433006, null#150052</t>
+  </si>
+  <si>
+    <t>SNOMED CT#430160002</t>
+  </si>
+  <si>
+    <t>mii-pr-icu-muv-pulmonalvaskulaerer-widerstandsindex</t>
+  </si>
+  <si>
+    <t>MII PR ICU MUV Pulmonalvaskulaerer Widerstandsindex</t>
+  </si>
+  <si>
+    <t>null#8834-4, null#276902009, null#152852</t>
+  </si>
+  <si>
     <t>mii-pr-icu-parameter-von-extrakorporalen-verfahren</t>
   </si>
   <si>
@@ -395,6 +557,18 @@
     <t>Quantityĵ, CodeableConceptĵ, integerĵ</t>
   </si>
   <si>
+    <t>mii-pr-icu-score-cam-icu</t>
+  </si>
+  <si>
+    <t>MII PR ICU Score CAM-ICU</t>
+  </si>
+  <si>
+    <t>null#99844-5, null#450740000</t>
+  </si>
+  <si>
+    <t>CodeableConceptĵ</t>
+  </si>
+  <si>
     <t>mii-pr-icu-score-faces-pain-scale-revised</t>
   </si>
   <si>
@@ -413,9 +587,6 @@
     <t>null#9269-2, null#248241002, null#153728</t>
   </si>
   <si>
-    <t>CodeableConceptĵ</t>
-  </si>
-  <si>
     <t>LOINC#9267-6</t>
   </si>
   <si>
@@ -425,6 +596,18 @@
     <t>LOINC#9270-0</t>
   </si>
   <si>
+    <t>mii-pr-icu-score-icdsc</t>
+  </si>
+  <si>
+    <t>MII PR ICU Score ICDSC</t>
+  </si>
+  <si>
+    <t>null#1351995008</t>
+  </si>
+  <si>
+    <t>integerĵ</t>
+  </si>
+  <si>
     <t>mii-pr-icu-score-numerische-ratingskala</t>
   </si>
   <si>
@@ -434,7 +617,46 @@
     <t>null#1284857008</t>
   </si>
   <si>
-    <t>integerĵ</t>
+    <t>mii-pr-icu-score-rass</t>
+  </si>
+  <si>
+    <t>MII PR ICU Score RASS</t>
+  </si>
+  <si>
+    <t>Observation Category Codes#exam</t>
+  </si>
+  <si>
+    <t>null#1345050000</t>
+  </si>
+  <si>
+    <t>dateTimeĵ</t>
+  </si>
+  <si>
+    <t>mii-pr-icu-score-sofa</t>
+  </si>
+  <si>
+    <t>MII PR ICU Score SOFA</t>
+  </si>
+  <si>
+    <t>null#96789-3, null#1187491009</t>
+  </si>
+  <si>
+    <t>LOINC#96823-0, SNOMED CT#xxxx</t>
+  </si>
+  <si>
+    <t>LOINC#96826-3, SNOMED CT#xxx</t>
+  </si>
+  <si>
+    <t>LOINC#96825-5, SNOMED CT#xxx</t>
+  </si>
+  <si>
+    <t>LOINC#96824-8, SNOMED CT#xxx</t>
+  </si>
+  <si>
+    <t>LOINC#96828-9, SNOMED CT#xxx</t>
+  </si>
+  <si>
+    <t>LOINC#96827-1, SNOMED CT#xxxx</t>
   </si>
   <si>
     <t>mii-pr-icu-score-visuelle-analogskala</t>
@@ -446,6 +668,90 @@
     <t>null#38214-3, null#443394008</t>
   </si>
   <si>
+    <t>mii-pr-icu-score-wong-baker-faces-schmerzskala</t>
+  </si>
+  <si>
+    <t>MII PR ICU Score Wong-Baker-FACES-Schmerzskala</t>
+  </si>
+  <si>
+    <t>Observation Category Codes#survey</t>
+  </si>
+  <si>
+    <t>null#38221-8, null#718581005</t>
+  </si>
+  <si>
+    <t>mii-pr-icu-score-zopa</t>
+  </si>
+  <si>
+    <t>MII PR ICU Score ZOPA</t>
+  </si>
+  <si>
+    <t>null#DGAI-ZOPA</t>
+  </si>
+  <si>
+    <t>mii-pr-icu-untersuchung-pupillenbefund</t>
+  </si>
+  <si>
+    <t>MII PR ICU Untersuchung Pupillenbefund</t>
+  </si>
+  <si>
+    <t>null#247010007, null#80310-6</t>
+  </si>
+  <si>
+    <t>dateTime, Period, Timing, instant</t>
+  </si>
+  <si>
+    <t>mii-pr-icu-untersuchung-pupillenform</t>
+  </si>
+  <si>
+    <t>MII PR ICU Untersuchung Pupillenform</t>
+  </si>
+  <si>
+    <t>null#363954009</t>
+  </si>
+  <si>
+    <t>mii-pr-icu-untersuchung-pupillengroesse</t>
+  </si>
+  <si>
+    <t>MII PR ICU Untersuchung Pupillengroesse</t>
+  </si>
+  <si>
+    <t>null#363953003</t>
+  </si>
+  <si>
+    <t>Quantityĵ, CodeableConceptĵ</t>
+  </si>
+  <si>
+    <t>mii-pr-icu-untersuchung-pupillenlichtreaktion-direkt</t>
+  </si>
+  <si>
+    <t>MII PR ICU Untersuchung Pupillenlichtreaktion Direkt</t>
+  </si>
+  <si>
+    <t>null#45832002</t>
+  </si>
+  <si>
+    <t>mii-pr-icu-untersuchung-pupillenlichtreaktion-indirekt</t>
+  </si>
+  <si>
+    <t>MII PR ICU Untersuchung Pupillenlichtreaktion Indirekt</t>
+  </si>
+  <si>
+    <t>null#84917001</t>
+  </si>
+  <si>
+    <t>mii-pr-icu-untersuchung-pupillensymmetrie</t>
+  </si>
+  <si>
+    <t>MII PR ICU Untersuchung Pupillensymmetrie</t>
+  </si>
+  <si>
+    <t>null#301942005</t>
+  </si>
+  <si>
+    <t>SNOMED CT#67019001</t>
+  </si>
+  <si>
     <t>mii-pr-icu-vent-atemwegsdruck-mittlerem-expiratorischem-gasfluss</t>
   </si>
   <si>
@@ -563,6 +869,15 @@
     <t>null#250819002, null#76334-2, null#16929632</t>
   </si>
   <si>
+    <t>mii-pr-icu-vent-einstellung-inspirationsdruck</t>
+  </si>
+  <si>
+    <t>MII PR ICU Einstellung Inspirationsdruck</t>
+  </si>
+  <si>
+    <t>null#76003-3, null#151972</t>
+  </si>
+  <si>
     <t>mii-pr-icu-vent-endexpiratorischer-kohlendioxidpartialdruck</t>
   </si>
   <si>
@@ -627,6 +942,18 @@
   </si>
   <si>
     <t>null#76531-3, null#151957</t>
+  </si>
+  <si>
+    <t>mii-pr-icu-vent-maximaler-inspiratorischer-beatmungsdruck</t>
+  </si>
+  <si>
+    <t>MII PR ICU Maximaler Inspiratorischer Beatmungsdruck</t>
+  </si>
+  <si>
+    <t>null#27913002, null#151973</t>
+  </si>
+  <si>
+    <t>https://www.medizininformatik-initiative.de/fhir/ext/modul-icu/ValueSet/mii-vs-icu-code-observation-beatmung-loinc (required)</t>
   </si>
   <si>
     <t>mii-pr-icu-vent-mechanische-atemfrequenz-beatmet</t>
@@ -859,7 +1186,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:K74"/>
+  <dimension ref="A1:K123"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -1430,19 +1757,19 @@
         <v>63</v>
       </c>
       <c r="C17" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D17" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E17" t="s" s="2">
         <v>64</v>
       </c>
-      <c r="D17" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E17" t="s" s="2">
+      <c r="F17" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="G17" t="s" s="2">
         <v>65</v>
-      </c>
-      <c r="F17" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="G17" t="s" s="2">
-        <v>17</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>18</v>
@@ -1465,7 +1792,7 @@
         <v>67</v>
       </c>
       <c r="C18" t="s" s="2">
-        <v>64</v>
+        <v>13</v>
       </c>
       <c r="D18" t="s" s="2">
         <v>14</v>
@@ -1500,7 +1827,7 @@
         <v>70</v>
       </c>
       <c r="C19" t="s" s="2">
-        <v>64</v>
+        <v>13</v>
       </c>
       <c r="D19" t="s" s="2">
         <v>14</v>
@@ -1535,7 +1862,7 @@
         <v>73</v>
       </c>
       <c r="C20" t="s" s="2">
-        <v>64</v>
+        <v>13</v>
       </c>
       <c r="D20" t="s" s="2">
         <v>14</v>
@@ -1570,7 +1897,7 @@
         <v>76</v>
       </c>
       <c r="C21" t="s" s="2">
-        <v>64</v>
+        <v>13</v>
       </c>
       <c r="D21" t="s" s="2">
         <v>14</v>
@@ -1605,7 +1932,7 @@
         <v>79</v>
       </c>
       <c r="C22" t="s" s="2">
-        <v>64</v>
+        <v>13</v>
       </c>
       <c r="D22" t="s" s="2">
         <v>14</v>
@@ -1640,13 +1967,13 @@
         <v>82</v>
       </c>
       <c r="C23" t="s" s="2">
-        <v>64</v>
+        <v>83</v>
       </c>
       <c r="D23" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E23" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F23" t="s" s="2">
         <v>16</v>
@@ -1669,19 +1996,19 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>64</v>
+        <v>83</v>
       </c>
       <c r="D24" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E24" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F24" t="s" s="2">
         <v>16</v>
@@ -1704,19 +2031,19 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C25" t="s" s="2">
-        <v>64</v>
+        <v>83</v>
       </c>
       <c r="D25" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E25" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F25" t="s" s="2">
         <v>16</v>
@@ -1739,13 +2066,13 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C26" t="s" s="2">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="D26" t="s" s="2">
         <v>14</v>
@@ -1754,16 +2081,16 @@
         <v>93</v>
       </c>
       <c r="F26" t="s" s="2">
-        <v>94</v>
+        <v>16</v>
       </c>
       <c r="G26" t="s" s="2">
         <v>17</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="I26" t="s" s="2">
-        <v>95</v>
+        <v>19</v>
       </c>
       <c r="J26" t="s" s="2">
         <v>14</v>
@@ -1774,13 +2101,13 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>14</v>
+        <v>94</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="C27" t="s" s="2">
-        <v>14</v>
+        <v>83</v>
       </c>
       <c r="D27" t="s" s="2">
         <v>14</v>
@@ -1789,10 +2116,10 @@
         <v>96</v>
       </c>
       <c r="F27" t="s" s="2">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>18</v>
@@ -1809,25 +2136,25 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>14</v>
+        <v>97</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="C28" t="s" s="2">
-        <v>14</v>
+        <v>83</v>
       </c>
       <c r="D28" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E28" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F28" t="s" s="2">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>18</v>
@@ -1844,25 +2171,25 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>14</v>
+        <v>100</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="C29" t="s" s="2">
-        <v>14</v>
+        <v>83</v>
       </c>
       <c r="D29" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E29" t="s" s="2">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="F29" t="s" s="2">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>18</v>
@@ -1879,22 +2206,22 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="C30" t="s" s="2">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="D30" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E30" t="s" s="2">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="F30" t="s" s="2">
-        <v>94</v>
+        <v>16</v>
       </c>
       <c r="G30" t="s" s="2">
         <v>17</v>
@@ -1914,22 +2241,22 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="C31" t="s" s="2">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="D31" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E31" t="s" s="2">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="F31" t="s" s="2">
-        <v>94</v>
+        <v>16</v>
       </c>
       <c r="G31" t="s" s="2">
         <v>17</v>
@@ -1949,28 +2276,28 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="C32" t="s" s="2">
-        <v>107</v>
+        <v>83</v>
       </c>
       <c r="D32" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E32" t="s" s="2">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="F32" t="s" s="2">
-        <v>94</v>
+        <v>16</v>
       </c>
       <c r="G32" t="s" s="2">
         <v>17</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>109</v>
+        <v>18</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>19</v>
@@ -1984,28 +2311,28 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C33" t="s" s="2">
-        <v>107</v>
+        <v>83</v>
       </c>
       <c r="D33" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E33" t="s" s="2">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F33" t="s" s="2">
-        <v>94</v>
+        <v>16</v>
       </c>
       <c r="G33" t="s" s="2">
         <v>17</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>109</v>
+        <v>18</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>19</v>
@@ -2019,22 +2346,22 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C34" t="s" s="2">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="D34" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E34" t="s" s="2">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F34" t="s" s="2">
-        <v>94</v>
+        <v>16</v>
       </c>
       <c r="G34" t="s" s="2">
         <v>17</v>
@@ -2054,34 +2381,34 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C35" t="s" s="2">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D35" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E35" t="s" s="2">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="F35" t="s" s="2">
-        <v>94</v>
+        <v>122</v>
       </c>
       <c r="G35" t="s" s="2">
         <v>17</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>109</v>
+        <v>14</v>
       </c>
       <c r="I35" t="s" s="2">
-        <v>19</v>
+        <v>123</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>120</v>
+        <v>14</v>
       </c>
       <c r="K35" t="s" s="2">
         <v>14</v>
@@ -2089,25 +2416,25 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>121</v>
+        <v>14</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C36" t="s" s="2">
-        <v>64</v>
+        <v>14</v>
       </c>
       <c r="D36" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E36" t="s" s="2">
-        <v>15</v>
+        <v>124</v>
       </c>
       <c r="F36" t="s" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>18</v>
@@ -2124,28 +2451,28 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>123</v>
+        <v>14</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="C37" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="D37" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E37" t="s" s="2">
         <v>125</v>
       </c>
-      <c r="D37" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E37" t="s" s="2">
-        <v>14</v>
-      </c>
       <c r="F37" t="s" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>126</v>
+        <v>18</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>19</v>
@@ -2159,25 +2486,25 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>127</v>
+        <v>14</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="C38" t="s" s="2">
-        <v>125</v>
+        <v>14</v>
       </c>
       <c r="D38" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E38" t="s" s="2">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="F38" t="s" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>18</v>
@@ -2194,22 +2521,22 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="C39" t="s" s="2">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="D39" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E39" t="s" s="2">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="F39" t="s" s="2">
-        <v>16</v>
+        <v>122</v>
       </c>
       <c r="G39" t="s" s="2">
         <v>17</v>
@@ -2229,28 +2556,28 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>14</v>
+        <v>130</v>
       </c>
       <c r="B40" t="s" s="2">
         <v>131</v>
       </c>
       <c r="C40" t="s" s="2">
-        <v>14</v>
+        <v>120</v>
       </c>
       <c r="D40" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E40" t="s" s="2">
-        <v>14</v>
+        <v>132</v>
       </c>
       <c r="F40" t="s" s="2">
-        <v>14</v>
+        <v>122</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>133</v>
+        <v>18</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>19</v>
@@ -2259,33 +2586,33 @@
         <v>14</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>134</v>
+        <v>14</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>14</v>
+        <v>133</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="C41" t="s" s="2">
-        <v>14</v>
+        <v>135</v>
       </c>
       <c r="D41" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E41" t="s" s="2">
-        <v>14</v>
+        <v>136</v>
       </c>
       <c r="F41" t="s" s="2">
-        <v>14</v>
+        <v>122</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>133</v>
+        <v>18</v>
       </c>
       <c r="I41" t="s" s="2">
         <v>19</v>
@@ -2294,33 +2621,33 @@
         <v>14</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>135</v>
+        <v>14</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>14</v>
+        <v>137</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="C42" t="s" s="2">
-        <v>14</v>
+        <v>135</v>
       </c>
       <c r="D42" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E42" t="s" s="2">
-        <v>14</v>
+        <v>139</v>
       </c>
       <c r="F42" t="s" s="2">
-        <v>14</v>
+        <v>122</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>133</v>
+        <v>18</v>
       </c>
       <c r="I42" t="s" s="2">
         <v>19</v>
@@ -2329,39 +2656,39 @@
         <v>14</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>136</v>
+        <v>14</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="C43" t="s" s="2">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="D43" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E43" t="s" s="2">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="F43" t="s" s="2">
-        <v>16</v>
+        <v>122</v>
       </c>
       <c r="G43" t="s" s="2">
         <v>17</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>140</v>
+        <v>18</v>
       </c>
       <c r="I43" t="s" s="2">
         <v>19</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>14</v>
+        <v>143</v>
       </c>
       <c r="K43" t="s" s="2">
         <v>14</v>
@@ -2369,28 +2696,28 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="C44" t="s" s="2">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="D44" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E44" t="s" s="2">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="F44" t="s" s="2">
-        <v>16</v>
+        <v>122</v>
       </c>
       <c r="G44" t="s" s="2">
         <v>17</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>18</v>
+        <v>147</v>
       </c>
       <c r="I44" t="s" s="2">
         <v>19</v>
@@ -2404,22 +2731,22 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="C45" t="s" s="2">
-        <v>146</v>
+        <v>135</v>
       </c>
       <c r="D45" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E45" t="s" s="2">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="F45" t="s" s="2">
-        <v>148</v>
+        <v>122</v>
       </c>
       <c r="G45" t="s" s="2">
         <v>17</v>
@@ -2439,28 +2766,28 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C46" t="s" s="2">
-        <v>146</v>
+        <v>135</v>
       </c>
       <c r="D46" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E46" t="s" s="2">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="F46" t="s" s="2">
-        <v>148</v>
+        <v>122</v>
       </c>
       <c r="G46" t="s" s="2">
         <v>17</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>18</v>
+        <v>147</v>
       </c>
       <c r="I46" t="s" s="2">
         <v>19</v>
@@ -2474,22 +2801,22 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C47" t="s" s="2">
-        <v>146</v>
+        <v>135</v>
       </c>
       <c r="D47" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E47" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="F47" t="s" s="2">
-        <v>16</v>
+        <v>122</v>
       </c>
       <c r="G47" t="s" s="2">
         <v>17</v>
@@ -2509,22 +2836,22 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C48" t="s" s="2">
-        <v>146</v>
+        <v>120</v>
       </c>
       <c r="D48" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E48" t="s" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="F48" t="s" s="2">
-        <v>16</v>
+        <v>122</v>
       </c>
       <c r="G48" t="s" s="2">
         <v>17</v>
@@ -2544,22 +2871,22 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C49" t="s" s="2">
-        <v>146</v>
+        <v>135</v>
       </c>
       <c r="D49" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E49" t="s" s="2">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="F49" t="s" s="2">
-        <v>16</v>
+        <v>122</v>
       </c>
       <c r="G49" t="s" s="2">
         <v>17</v>
@@ -2579,34 +2906,34 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C50" t="s" s="2">
-        <v>146</v>
+        <v>165</v>
       </c>
       <c r="D50" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E50" t="s" s="2">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="F50" t="s" s="2">
-        <v>164</v>
+        <v>122</v>
       </c>
       <c r="G50" t="s" s="2">
         <v>17</v>
       </c>
       <c r="H50" t="s" s="2">
-        <v>18</v>
+        <v>147</v>
       </c>
       <c r="I50" t="s" s="2">
         <v>19</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>14</v>
+        <v>167</v>
       </c>
       <c r="K50" t="s" s="2">
         <v>14</v>
@@ -2614,22 +2941,22 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="C51" t="s" s="2">
-        <v>146</v>
+        <v>135</v>
       </c>
       <c r="D51" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E51" t="s" s="2">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="F51" t="s" s="2">
-        <v>164</v>
+        <v>122</v>
       </c>
       <c r="G51" t="s" s="2">
         <v>17</v>
@@ -2641,7 +2968,7 @@
         <v>19</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>14</v>
+        <v>171</v>
       </c>
       <c r="K51" t="s" s="2">
         <v>14</v>
@@ -2649,22 +2976,22 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="C52" t="s" s="2">
-        <v>146</v>
+        <v>135</v>
       </c>
       <c r="D52" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E52" t="s" s="2">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="F52" t="s" s="2">
-        <v>164</v>
+        <v>122</v>
       </c>
       <c r="G52" t="s" s="2">
         <v>17</v>
@@ -2684,19 +3011,19 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="C53" t="s" s="2">
-        <v>146</v>
+        <v>83</v>
       </c>
       <c r="D53" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E53" t="s" s="2">
-        <v>173</v>
+        <v>15</v>
       </c>
       <c r="F53" t="s" s="2">
         <v>16</v>
@@ -2719,28 +3046,28 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="C54" t="s" s="2">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="D54" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E54" t="s" s="2">
-        <v>176</v>
+        <v>14</v>
       </c>
       <c r="F54" t="s" s="2">
-        <v>148</v>
+        <v>16</v>
       </c>
       <c r="G54" t="s" s="2">
         <v>17</v>
       </c>
       <c r="H54" t="s" s="2">
-        <v>18</v>
+        <v>180</v>
       </c>
       <c r="I54" t="s" s="2">
         <v>19</v>
@@ -2754,28 +3081,28 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="C55" t="s" s="2">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="D55" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E55" t="s" s="2">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="F55" t="s" s="2">
-        <v>148</v>
+        <v>16</v>
       </c>
       <c r="G55" t="s" s="2">
         <v>17</v>
       </c>
       <c r="H55" t="s" s="2">
-        <v>18</v>
+        <v>184</v>
       </c>
       <c r="I55" t="s" s="2">
         <v>19</v>
@@ -2789,28 +3116,28 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>180</v>
+        <v>14</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C56" t="s" s="2">
-        <v>146</v>
+        <v>14</v>
       </c>
       <c r="D56" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E56" t="s" s="2">
-        <v>182</v>
+        <v>14</v>
       </c>
       <c r="F56" t="s" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H56" t="s" s="2">
-        <v>18</v>
+        <v>184</v>
       </c>
       <c r="I56" t="s" s="2">
         <v>19</v>
@@ -2824,28 +3151,28 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>183</v>
+        <v>14</v>
       </c>
       <c r="B57" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="C57" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="D57" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E57" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="F57" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="G57" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="H57" t="s" s="2">
         <v>184</v>
-      </c>
-      <c r="C57" t="s" s="2">
-        <v>185</v>
-      </c>
-      <c r="D57" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E57" t="s" s="2">
-        <v>186</v>
-      </c>
-      <c r="F57" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="G57" t="s" s="2">
-        <v>17</v>
-      </c>
-      <c r="H57" t="s" s="2">
-        <v>18</v>
       </c>
       <c r="I57" t="s" s="2">
         <v>19</v>
@@ -2859,28 +3186,28 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>187</v>
+        <v>14</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="C58" t="s" s="2">
-        <v>146</v>
+        <v>14</v>
       </c>
       <c r="D58" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E58" t="s" s="2">
-        <v>189</v>
+        <v>14</v>
       </c>
       <c r="F58" t="s" s="2">
-        <v>164</v>
+        <v>14</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H58" t="s" s="2">
-        <v>18</v>
+        <v>184</v>
       </c>
       <c r="I58" t="s" s="2">
         <v>19</v>
@@ -2894,28 +3221,28 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>190</v>
+        <v>14</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>191</v>
+        <v>182</v>
       </c>
       <c r="C59" t="s" s="2">
-        <v>185</v>
+        <v>14</v>
       </c>
       <c r="D59" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E59" t="s" s="2">
-        <v>192</v>
+        <v>14</v>
       </c>
       <c r="F59" t="s" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H59" t="s" s="2">
-        <v>18</v>
+        <v>184</v>
       </c>
       <c r="I59" t="s" s="2">
         <v>19</v>
@@ -2929,22 +3256,22 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="C60" t="s" s="2">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="D60" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E60" t="s" s="2">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="F60" t="s" s="2">
-        <v>164</v>
+        <v>16</v>
       </c>
       <c r="G60" t="s" s="2">
         <v>17</v>
@@ -2964,22 +3291,22 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="C61" t="s" s="2">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="D61" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E61" t="s" s="2">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="F61" t="s" s="2">
-        <v>148</v>
+        <v>16</v>
       </c>
       <c r="G61" t="s" s="2">
         <v>17</v>
@@ -2999,28 +3326,28 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>199</v>
+        <v>14</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>200</v>
+        <v>189</v>
       </c>
       <c r="C62" t="s" s="2">
-        <v>146</v>
+        <v>14</v>
       </c>
       <c r="D62" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E62" t="s" s="2">
-        <v>201</v>
+        <v>14</v>
       </c>
       <c r="F62" t="s" s="2">
-        <v>164</v>
+        <v>14</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H62" t="s" s="2">
-        <v>18</v>
+        <v>184</v>
       </c>
       <c r="I62" t="s" s="2">
         <v>19</v>
@@ -3029,33 +3356,33 @@
         <v>14</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>14</v>
+        <v>191</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>202</v>
+        <v>14</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>203</v>
+        <v>189</v>
       </c>
       <c r="C63" t="s" s="2">
-        <v>146</v>
+        <v>14</v>
       </c>
       <c r="D63" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E63" t="s" s="2">
-        <v>204</v>
+        <v>14</v>
       </c>
       <c r="F63" t="s" s="2">
-        <v>164</v>
+        <v>14</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H63" t="s" s="2">
-        <v>18</v>
+        <v>184</v>
       </c>
       <c r="I63" t="s" s="2">
         <v>19</v>
@@ -3064,33 +3391,33 @@
         <v>14</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>14</v>
+        <v>192</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>205</v>
+        <v>14</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>206</v>
+        <v>189</v>
       </c>
       <c r="C64" t="s" s="2">
-        <v>146</v>
+        <v>14</v>
       </c>
       <c r="D64" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E64" t="s" s="2">
-        <v>207</v>
+        <v>14</v>
       </c>
       <c r="F64" t="s" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H64" t="s" s="2">
-        <v>18</v>
+        <v>184</v>
       </c>
       <c r="I64" t="s" s="2">
         <v>19</v>
@@ -3099,24 +3426,24 @@
         <v>14</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>14</v>
+        <v>193</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>208</v>
+        <v>194</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>209</v>
+        <v>195</v>
       </c>
       <c r="C65" t="s" s="2">
-        <v>14</v>
+        <v>179</v>
       </c>
       <c r="D65" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E65" t="s" s="2">
-        <v>210</v>
+        <v>196</v>
       </c>
       <c r="F65" t="s" s="2">
         <v>16</v>
@@ -3125,7 +3452,7 @@
         <v>17</v>
       </c>
       <c r="H65" t="s" s="2">
-        <v>18</v>
+        <v>197</v>
       </c>
       <c r="I65" t="s" s="2">
         <v>19</v>
@@ -3139,28 +3466,28 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>211</v>
+        <v>14</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>212</v>
+        <v>195</v>
       </c>
       <c r="C66" t="s" s="2">
-        <v>146</v>
+        <v>14</v>
       </c>
       <c r="D66" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E66" t="s" s="2">
-        <v>213</v>
+        <v>14</v>
       </c>
       <c r="F66" t="s" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H66" t="s" s="2">
-        <v>18</v>
+        <v>197</v>
       </c>
       <c r="I66" t="s" s="2">
         <v>19</v>
@@ -3174,28 +3501,28 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>214</v>
+        <v>14</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>215</v>
+        <v>195</v>
       </c>
       <c r="C67" t="s" s="2">
-        <v>146</v>
+        <v>14</v>
       </c>
       <c r="D67" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E67" t="s" s="2">
-        <v>216</v>
+        <v>14</v>
       </c>
       <c r="F67" t="s" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H67" t="s" s="2">
-        <v>18</v>
+        <v>197</v>
       </c>
       <c r="I67" t="s" s="2">
         <v>19</v>
@@ -3209,28 +3536,28 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>217</v>
+        <v>14</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>218</v>
+        <v>195</v>
       </c>
       <c r="C68" t="s" s="2">
-        <v>146</v>
+        <v>14</v>
       </c>
       <c r="D68" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E68" t="s" s="2">
-        <v>219</v>
+        <v>14</v>
       </c>
       <c r="F68" t="s" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H68" t="s" s="2">
-        <v>18</v>
+        <v>197</v>
       </c>
       <c r="I68" t="s" s="2">
         <v>19</v>
@@ -3244,28 +3571,28 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>220</v>
+        <v>14</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>221</v>
+        <v>195</v>
       </c>
       <c r="C69" t="s" s="2">
-        <v>146</v>
+        <v>14</v>
       </c>
       <c r="D69" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E69" t="s" s="2">
-        <v>222</v>
+        <v>14</v>
       </c>
       <c r="F69" t="s" s="2">
-        <v>164</v>
+        <v>14</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H69" t="s" s="2">
-        <v>18</v>
+        <v>197</v>
       </c>
       <c r="I69" t="s" s="2">
         <v>19</v>
@@ -3279,28 +3606,28 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>223</v>
+        <v>14</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>224</v>
+        <v>195</v>
       </c>
       <c r="C70" t="s" s="2">
-        <v>146</v>
+        <v>14</v>
       </c>
       <c r="D70" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E70" t="s" s="2">
-        <v>225</v>
+        <v>14</v>
       </c>
       <c r="F70" t="s" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H70" t="s" s="2">
-        <v>18</v>
+        <v>197</v>
       </c>
       <c r="I70" t="s" s="2">
         <v>19</v>
@@ -3314,28 +3641,28 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>226</v>
+        <v>14</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>227</v>
+        <v>195</v>
       </c>
       <c r="C71" t="s" s="2">
-        <v>146</v>
+        <v>14</v>
       </c>
       <c r="D71" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E71" t="s" s="2">
-        <v>228</v>
+        <v>14</v>
       </c>
       <c r="F71" t="s" s="2">
-        <v>148</v>
+        <v>14</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H71" t="s" s="2">
-        <v>18</v>
+        <v>197</v>
       </c>
       <c r="I71" t="s" s="2">
         <v>19</v>
@@ -3349,28 +3676,28 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>229</v>
+        <v>14</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>230</v>
+        <v>195</v>
       </c>
       <c r="C72" t="s" s="2">
-        <v>146</v>
+        <v>14</v>
       </c>
       <c r="D72" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E72" t="s" s="2">
-        <v>231</v>
+        <v>14</v>
       </c>
       <c r="F72" t="s" s="2">
-        <v>148</v>
+        <v>14</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H72" t="s" s="2">
-        <v>18</v>
+        <v>197</v>
       </c>
       <c r="I72" t="s" s="2">
         <v>19</v>
@@ -3384,28 +3711,28 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>232</v>
+        <v>14</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>233</v>
+        <v>195</v>
       </c>
       <c r="C73" t="s" s="2">
-        <v>146</v>
+        <v>14</v>
       </c>
       <c r="D73" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E73" t="s" s="2">
-        <v>234</v>
+        <v>14</v>
       </c>
       <c r="F73" t="s" s="2">
-        <v>148</v>
+        <v>14</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H73" t="s" s="2">
-        <v>18</v>
+        <v>197</v>
       </c>
       <c r="I73" t="s" s="2">
         <v>19</v>
@@ -3419,36 +3746,1751 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="B74" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="C74" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="D74" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E74" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="F74" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="G74" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="H74" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="I74" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J74" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K74" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="B75" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="C75" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="D75" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E75" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="F75" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="G75" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="H75" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="I75" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J75" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K75" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="B76" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="C76" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="D76" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E76" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="F76" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="G76" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="H76" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="I76" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J76" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K76" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="B77" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="C77" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="D77" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E77" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="F77" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="G77" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="H77" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="I77" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J77" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K77" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="B78" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="C78" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="D78" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E78" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="F78" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="G78" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="H78" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="I78" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J78" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K78" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="B79" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="C79" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="D79" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E79" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="F79" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="G79" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="H79" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="I79" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J79" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K79" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="B80" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="C80" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="D80" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E80" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="F80" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="G80" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="H80" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="I80" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J80" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K80" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="B81" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="C81" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="D81" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E81" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="F81" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="G81" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="H81" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="I81" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J81" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K81" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="B82" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="C82" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="D82" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E82" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="F82" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="G82" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="H82" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="I82" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J82" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K82" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="B83" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="C83" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="D83" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E83" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="F83" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="G83" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="H83" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="I83" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J83" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K83" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="B84" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="C84" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="D84" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E84" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="F84" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="G84" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="H84" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="I84" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J84" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K84" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="B85" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="C85" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="D85" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E85" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="F85" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="G85" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="H85" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="I85" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J85" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K85" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="B86" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="C86" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="D86" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E86" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="F86" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="G86" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="H86" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="I86" t="s" s="2">
+        <v>123</v>
+      </c>
+      <c r="J86" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K86" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="B87" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="C87" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="D87" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E87" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="F87" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="G87" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="H87" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="I87" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J87" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K87" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="B88" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="C88" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="D88" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E88" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="F88" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="G88" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="H88" t="s" s="2">
         <v>235</v>
       </c>
-      <c r="B74" t="s" s="2">
+      <c r="I88" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J88" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K88" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="s" s="2">
         <v>236</v>
       </c>
-      <c r="C74" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="D74" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E74" t="s" s="2">
+      <c r="B89" t="s" s="2">
         <v>237</v>
       </c>
-      <c r="F74" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="G74" t="s" s="2">
-        <v>17</v>
-      </c>
-      <c r="H74" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="I74" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="J74" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="K74" t="s" s="2">
+      <c r="C89" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="D89" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E89" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="F89" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="G89" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="H89" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="I89" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J89" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K89" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="B90" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="C90" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="D90" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E90" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="F90" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="G90" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="H90" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="I90" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J90" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K90" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="B91" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="C91" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="D91" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E91" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="F91" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="G91" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="H91" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="I91" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J91" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="K91" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="B92" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="C92" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="D92" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E92" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="F92" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="G92" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="H92" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="I92" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J92" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K92" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="B93" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="C93" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="D93" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E93" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="F93" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="G93" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="H93" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="I93" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J93" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K93" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="B94" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="C94" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="D94" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E94" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="F94" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="G94" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="H94" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="I94" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J94" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K94" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="B95" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="C95" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="D95" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E95" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="F95" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="G95" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="H95" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="I95" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J95" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K95" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="B96" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="C96" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="D96" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E96" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="F96" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="G96" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="H96" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="I96" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J96" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K96" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="B97" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="C97" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="D97" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E97" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="F97" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="G97" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="H97" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="I97" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J97" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K97" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="B98" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="C98" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="D98" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E98" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="F98" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="G98" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="H98" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="I98" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J98" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K98" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="B99" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="C99" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="D99" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E99" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="F99" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="G99" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="H99" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="I99" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J99" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K99" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="B100" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="C100" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="D100" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E100" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="F100" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="G100" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="H100" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="I100" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J100" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K100" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="B101" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="C101" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="D101" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E101" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="F101" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="G101" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="H101" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="I101" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J101" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K101" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="B102" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="C102" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="D102" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E102" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="F102" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="G102" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="H102" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="I102" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J102" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K102" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="B103" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="C103" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="D103" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E103" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="F103" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="G103" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="H103" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="I103" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J103" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K103" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="B104" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="C104" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="D104" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E104" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="F104" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="G104" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="H104" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="I104" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J104" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K104" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="B105" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="C105" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="D105" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E105" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="F105" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="G105" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="H105" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="I105" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J105" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K105" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="B106" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="C106" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="D106" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E106" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="F106" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="G106" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="H106" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="I106" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J106" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K106" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="B107" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="C107" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="D107" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E107" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="F107" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="G107" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="H107" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="I107" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J107" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K107" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="B108" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="C108" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="D108" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E108" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="F108" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="G108" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="H108" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="I108" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J108" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K108" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="B109" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="C109" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="D109" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E109" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="F109" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="G109" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="H109" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="I109" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J109" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K109" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="B110" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="C110" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="D110" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E110" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="F110" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="G110" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="H110" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="I110" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J110" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K110" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="B111" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="C111" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="D111" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E111" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="F111" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="G111" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="H111" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="I111" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J111" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K111" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="B112" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="C112" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="D112" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E112" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="F112" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="G112" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="H112" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="I112" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J112" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K112" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="B113" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="C113" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="D113" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E113" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="F113" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="G113" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="H113" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="I113" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J113" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K113" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="B114" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="C114" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="D114" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E114" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="F114" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="G114" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="H114" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="I114" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J114" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K114" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="B115" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="C115" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="D115" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E115" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="F115" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="G115" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="H115" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="I115" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J115" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K115" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="B116" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="C116" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="D116" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E116" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="F116" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="G116" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="H116" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="I116" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J116" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K116" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="B117" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="C117" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="D117" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E117" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="F117" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="G117" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="H117" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="I117" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J117" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K117" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="B118" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="C118" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="D118" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E118" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="F118" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="G118" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="H118" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="I118" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J118" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K118" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="B119" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="C119" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="D119" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E119" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="F119" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="G119" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="H119" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="I119" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J119" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K119" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="B120" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="C120" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="D120" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E120" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="F120" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="G120" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="H120" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="I120" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J120" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K120" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="B121" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="C121" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="D121" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E121" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="F121" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="G121" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="H121" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="I121" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J121" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K121" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="B122" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="C122" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="D122" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E122" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="F122" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="G122" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="H122" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="I122" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J122" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K122" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="B123" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="C123" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="D123" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E123" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="F123" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="G123" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="H123" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="I123" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J123" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K123" t="s" s="2">
         <v>14</v>
       </c>
     </row>
